--- a/downloads/Mio_franchise_stores.xlsx
+++ b/downloads/Mio_franchise_stores.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RajeevK\Desktop\FranchiseIQ\downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Franchise_IQ\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="779">
   <si>
     <t>Sales</t>
   </si>
@@ -2361,6 +2361,12 @@
   </si>
   <si>
     <t>Region</t>
+  </si>
+  <si>
+    <t>From Date</t>
+  </si>
+  <si>
+    <t>To Date</t>
   </si>
 </sst>
 </file>
@@ -2420,7 +2426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2429,6 +2435,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10403,7 +10410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K385"/>
+  <dimension ref="A1:M385"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="12.90625" customWidth="1"/>
@@ -10412,9 +10419,10 @@
     <col min="5" max="5" width="12.36328125" customWidth="1"/>
     <col min="6" max="6" width="13.54296875" customWidth="1"/>
     <col min="11" max="11" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -10448,8 +10456,14 @@
       <c r="K1" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L1" t="s">
+        <v>777</v>
+      </c>
+      <c r="M1" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1000007545</v>
       </c>
@@ -10484,8 +10498,14 @@
         <f>VLOOKUP(A2,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L2" s="4">
+        <v>45901</v>
+      </c>
+      <c r="M2" s="4">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1000011213</v>
       </c>
@@ -10520,8 +10540,16 @@
         <f>VLOOKUP(A3,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3" s="4">
+        <f>$L$2</f>
+        <v>45901</v>
+      </c>
+      <c r="M3" s="4">
+        <f>$M$2</f>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1000011214</v>
       </c>
@@ -10556,8 +10584,16 @@
         <f>VLOOKUP(A4,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L4" s="4">
+        <f t="shared" ref="L4:L67" si="0">$L$2</f>
+        <v>45901</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" ref="M4:M67" si="1">$M$2</f>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1000011215</v>
       </c>
@@ -10592,8 +10628,16 @@
         <f>VLOOKUP(A5,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M5" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>1000011216</v>
       </c>
@@ -10628,8 +10672,16 @@
         <f>VLOOKUP(A6,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L6" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M6" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>1000011218</v>
       </c>
@@ -10664,8 +10716,16 @@
         <f>VLOOKUP(A7,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L7" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M7" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>1000011220</v>
       </c>
@@ -10700,8 +10760,16 @@
         <f>VLOOKUP(A8,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L8" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M8" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1000011223</v>
       </c>
@@ -10736,8 +10804,16 @@
         <f>VLOOKUP(A9,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L9" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M9" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>1000011224</v>
       </c>
@@ -10772,8 +10848,16 @@
         <f>VLOOKUP(A10,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L10" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M10" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>1000011225</v>
       </c>
@@ -10808,8 +10892,16 @@
         <f>VLOOKUP(A11,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L11" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M11" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>1000011228</v>
       </c>
@@ -10844,8 +10936,16 @@
         <f>VLOOKUP(A12,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L12" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M12" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>1000011230</v>
       </c>
@@ -10880,8 +10980,16 @@
         <f>VLOOKUP(A13,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L13" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M13" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>1000011232</v>
       </c>
@@ -10916,8 +11024,16 @@
         <f>VLOOKUP(A14,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L14" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>1000011233</v>
       </c>
@@ -10952,8 +11068,16 @@
         <f>VLOOKUP(A15,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L15" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M15" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>1000011235</v>
       </c>
@@ -10988,8 +11112,16 @@
         <f>VLOOKUP(A16,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L16" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M16" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>1000011236</v>
       </c>
@@ -11024,8 +11156,16 @@
         <f>VLOOKUP(A17,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L17" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M17" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>1000011237</v>
       </c>
@@ -11060,8 +11200,16 @@
         <f>VLOOKUP(A18,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L18" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M18" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>1000011238</v>
       </c>
@@ -11096,8 +11244,16 @@
         <f>VLOOKUP(A19,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L19" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M19" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>1000011239</v>
       </c>
@@ -11132,8 +11288,16 @@
         <f>VLOOKUP(A20,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L20" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M20" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>1000011240</v>
       </c>
@@ -11168,8 +11332,16 @@
         <f>VLOOKUP(A21,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L21" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M21" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>1000011241</v>
       </c>
@@ -11204,8 +11376,16 @@
         <f>VLOOKUP(A22,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L22" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M22" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>1000011242</v>
       </c>
@@ -11240,8 +11420,16 @@
         <f>VLOOKUP(A23,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L23" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M23" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>1000011243</v>
       </c>
@@ -11276,8 +11464,16 @@
         <f>VLOOKUP(A24,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L24" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M24" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>1000011245</v>
       </c>
@@ -11312,8 +11508,16 @@
         <f>VLOOKUP(A25,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L25" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M25" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>1000011246</v>
       </c>
@@ -11348,8 +11552,16 @@
         <f>VLOOKUP(A26,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L26" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M26" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>1000011247</v>
       </c>
@@ -11384,8 +11596,16 @@
         <f>VLOOKUP(A27,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L27" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M27" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>1000011249</v>
       </c>
@@ -11420,8 +11640,16 @@
         <f>VLOOKUP(A28,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L28" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M28" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>1000011250</v>
       </c>
@@ -11456,8 +11684,16 @@
         <f>VLOOKUP(A29,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L29" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M29" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>1000011252</v>
       </c>
@@ -11492,8 +11728,16 @@
         <f>VLOOKUP(A30,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L30" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M30" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>1000011255</v>
       </c>
@@ -11528,8 +11772,16 @@
         <f>VLOOKUP(A31,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L31" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M31" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>1000011257</v>
       </c>
@@ -11564,8 +11816,16 @@
         <f>VLOOKUP(A32,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L32" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M32" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>1000011258</v>
       </c>
@@ -11600,8 +11860,16 @@
         <f>VLOOKUP(A33,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L33" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M33" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>1000011259</v>
       </c>
@@ -11636,8 +11904,16 @@
         <f>VLOOKUP(A34,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L34" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M34" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>1000011260</v>
       </c>
@@ -11672,8 +11948,16 @@
         <f>VLOOKUP(A35,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L35" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M35" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>1000011261</v>
       </c>
@@ -11708,8 +11992,16 @@
         <f>VLOOKUP(A36,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L36" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M36" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>1000011262</v>
       </c>
@@ -11744,8 +12036,16 @@
         <f>VLOOKUP(A37,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L37" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M37" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>1000011264</v>
       </c>
@@ -11780,8 +12080,16 @@
         <f>VLOOKUP(A38,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L38" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M38" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>1000011265</v>
       </c>
@@ -11816,8 +12124,16 @@
         <f>VLOOKUP(A39,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L39" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M39" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>1000011266</v>
       </c>
@@ -11852,8 +12168,16 @@
         <f>VLOOKUP(A40,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L40" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M40" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>1000011267</v>
       </c>
@@ -11888,8 +12212,16 @@
         <f>VLOOKUP(A41,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L41" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M41" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>1000011268</v>
       </c>
@@ -11924,8 +12256,16 @@
         <f>VLOOKUP(A42,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L42" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M42" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>1000011269</v>
       </c>
@@ -11960,8 +12300,16 @@
         <f>VLOOKUP(A43,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L43" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M43" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>1000011270</v>
       </c>
@@ -11996,8 +12344,16 @@
         <f>VLOOKUP(A44,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L44" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M44" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>1000011271</v>
       </c>
@@ -12032,8 +12388,16 @@
         <f>VLOOKUP(A45,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L45" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M45" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>1000011272</v>
       </c>
@@ -12068,8 +12432,16 @@
         <f>VLOOKUP(A46,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L46" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M46" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>1000011273</v>
       </c>
@@ -12104,8 +12476,16 @@
         <f>VLOOKUP(A47,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L47" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M47" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>1000011279</v>
       </c>
@@ -12140,8 +12520,16 @@
         <f>VLOOKUP(A48,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L48" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M48" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>1000011301</v>
       </c>
@@ -12176,8 +12564,16 @@
         <f>VLOOKUP(A49,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L49" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M49" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>1000011312</v>
       </c>
@@ -12212,8 +12608,16 @@
         <f>VLOOKUP(A50,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L50" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M50" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>1000011323</v>
       </c>
@@ -12248,8 +12652,16 @@
         <f>VLOOKUP(A51,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L51" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M51" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>1000011324</v>
       </c>
@@ -12284,8 +12696,16 @@
         <f>VLOOKUP(A52,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L52" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M52" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>1000011335</v>
       </c>
@@ -12320,8 +12740,16 @@
         <f>VLOOKUP(A53,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L53" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M53" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>1000011346</v>
       </c>
@@ -12356,8 +12784,16 @@
         <f>VLOOKUP(A54,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L54" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M54" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>1000011357</v>
       </c>
@@ -12392,8 +12828,16 @@
         <f>VLOOKUP(A55,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L55" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M55" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>1000011368</v>
       </c>
@@ -12428,8 +12872,16 @@
         <f>VLOOKUP(A56,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L56" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M56" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>1000011379</v>
       </c>
@@ -12464,8 +12916,16 @@
         <f>VLOOKUP(A57,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L57" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M57" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>1000011390</v>
       </c>
@@ -12500,8 +12960,16 @@
         <f>VLOOKUP(A58,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L58" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M58" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>1000011391</v>
       </c>
@@ -12536,8 +13004,16 @@
         <f>VLOOKUP(A59,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L59" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M59" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>1000011394</v>
       </c>
@@ -12572,8 +13048,16 @@
         <f>VLOOKUP(A60,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L60" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M60" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>1000011397</v>
       </c>
@@ -12608,8 +13092,16 @@
         <f>VLOOKUP(A61,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L61" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M61" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>1000011399</v>
       </c>
@@ -12644,8 +13136,16 @@
         <f>VLOOKUP(A62,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L62" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M62" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>1000011401</v>
       </c>
@@ -12680,8 +13180,16 @@
         <f>VLOOKUP(A63,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L63" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M63" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>1000011404</v>
       </c>
@@ -12716,8 +13224,16 @@
         <f>VLOOKUP(A64,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L64" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M64" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>1000011405</v>
       </c>
@@ -12752,8 +13268,16 @@
         <f>VLOOKUP(A65,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L65" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M65" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>1000011407</v>
       </c>
@@ -12788,8 +13312,16 @@
         <f>VLOOKUP(A66,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L66" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M66" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>1000011408</v>
       </c>
@@ -12824,8 +13356,16 @@
         <f>VLOOKUP(A67,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L67" s="4">
+        <f t="shared" si="0"/>
+        <v>45901</v>
+      </c>
+      <c r="M67" s="4">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>1000011409</v>
       </c>
@@ -12860,8 +13400,16 @@
         <f>VLOOKUP(A68,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L68" s="4">
+        <f t="shared" ref="L68:L131" si="2">$L$2</f>
+        <v>45901</v>
+      </c>
+      <c r="M68" s="4">
+        <f t="shared" ref="M68:M131" si="3">$M$2</f>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>1000011410</v>
       </c>
@@ -12896,8 +13444,16 @@
         <f>VLOOKUP(A69,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L69" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M69" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>1000011411</v>
       </c>
@@ -12932,8 +13488,16 @@
         <f>VLOOKUP(A70,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L70" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M70" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>1000011412</v>
       </c>
@@ -12968,8 +13532,16 @@
         <f>VLOOKUP(A71,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L71" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M71" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>1000011413</v>
       </c>
@@ -13004,8 +13576,16 @@
         <f>VLOOKUP(A72,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L72" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M72" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>1000011414</v>
       </c>
@@ -13040,8 +13620,16 @@
         <f>VLOOKUP(A73,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L73" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M73" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>1000011416</v>
       </c>
@@ -13076,8 +13664,16 @@
         <f>VLOOKUP(A74,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L74" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M74" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>1000011417</v>
       </c>
@@ -13112,8 +13708,16 @@
         <f>VLOOKUP(A75,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L75" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M75" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>1000011419</v>
       </c>
@@ -13148,8 +13752,16 @@
         <f>VLOOKUP(A76,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L76" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M76" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>1000011420</v>
       </c>
@@ -13184,8 +13796,16 @@
         <f>VLOOKUP(A77,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L77" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M77" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>1000011422</v>
       </c>
@@ -13220,8 +13840,16 @@
         <f>VLOOKUP(A78,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L78" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M78" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>1000011424</v>
       </c>
@@ -13256,8 +13884,16 @@
         <f>VLOOKUP(A79,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L79" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M79" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>1000011425</v>
       </c>
@@ -13292,8 +13928,16 @@
         <f>VLOOKUP(A80,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L80" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M80" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>1000011426</v>
       </c>
@@ -13328,8 +13972,16 @@
         <f>VLOOKUP(A81,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L81" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M81" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>1000011427</v>
       </c>
@@ -13364,8 +14016,16 @@
         <f>VLOOKUP(A82,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L82" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M82" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>1000011428</v>
       </c>
@@ -13400,8 +14060,16 @@
         <f>VLOOKUP(A83,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L83" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M83" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>1000011429</v>
       </c>
@@ -13436,8 +14104,16 @@
         <f>VLOOKUP(A84,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L84" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M84" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>1000011430</v>
       </c>
@@ -13472,8 +14148,16 @@
         <f>VLOOKUP(A85,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L85" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M85" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>1000011431</v>
       </c>
@@ -13508,8 +14192,16 @@
         <f>VLOOKUP(A86,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L86" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M86" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>1000011432</v>
       </c>
@@ -13544,8 +14236,16 @@
         <f>VLOOKUP(A87,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L87" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M87" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>1000011433</v>
       </c>
@@ -13580,8 +14280,16 @@
         <f>VLOOKUP(A88,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L88" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M88" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>1000011434</v>
       </c>
@@ -13616,8 +14324,16 @@
         <f>VLOOKUP(A89,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L89" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M89" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>1000011435</v>
       </c>
@@ -13652,8 +14368,16 @@
         <f>VLOOKUP(A90,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L90" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M90" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>1000011436</v>
       </c>
@@ -13688,8 +14412,16 @@
         <f>VLOOKUP(A91,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L91" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M91" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>1000011437</v>
       </c>
@@ -13724,8 +14456,16 @@
         <f>VLOOKUP(A92,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L92" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M92" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>1000011438</v>
       </c>
@@ -13760,8 +14500,16 @@
         <f>VLOOKUP(A93,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L93" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M93" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>1000011439</v>
       </c>
@@ -13796,8 +14544,16 @@
         <f>VLOOKUP(A94,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L94" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M94" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>1000011440</v>
       </c>
@@ -13832,8 +14588,16 @@
         <f>VLOOKUP(A95,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L95" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M95" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>1000011441</v>
       </c>
@@ -13868,8 +14632,16 @@
         <f>VLOOKUP(A96,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L96" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M96" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>1000011443</v>
       </c>
@@ -13904,8 +14676,16 @@
         <f>VLOOKUP(A97,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L97" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M97" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>1000011444</v>
       </c>
@@ -13940,8 +14720,16 @@
         <f>VLOOKUP(A98,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L98" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M98" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>1000011445</v>
       </c>
@@ -13976,8 +14764,16 @@
         <f>VLOOKUP(A99,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L99" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M99" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>1000011446</v>
       </c>
@@ -14012,8 +14808,16 @@
         <f>VLOOKUP(A100,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L100" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M100" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>1000011447</v>
       </c>
@@ -14048,8 +14852,16 @@
         <f>VLOOKUP(A101,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L101" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M101" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>1000011448</v>
       </c>
@@ -14084,8 +14896,16 @@
         <f>VLOOKUP(A102,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L102" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M102" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>1000011449</v>
       </c>
@@ -14120,8 +14940,16 @@
         <f>VLOOKUP(A103,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L103" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M103" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>1000011450</v>
       </c>
@@ -14156,8 +14984,16 @@
         <f>VLOOKUP(A104,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L104" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M104" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>1000011451</v>
       </c>
@@ -14192,8 +15028,16 @@
         <f>VLOOKUP(A105,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L105" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M105" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>1000011453</v>
       </c>
@@ -14228,8 +15072,16 @@
         <f>VLOOKUP(A106,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L106" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M106" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>1000011454</v>
       </c>
@@ -14264,8 +15116,16 @@
         <f>VLOOKUP(A107,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L107" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M107" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>1000011455</v>
       </c>
@@ -14300,8 +15160,16 @@
         <f>VLOOKUP(A108,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L108" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M108" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>1000011456</v>
       </c>
@@ -14336,8 +15204,16 @@
         <f>VLOOKUP(A109,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L109" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M109" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>1000011457</v>
       </c>
@@ -14372,8 +15248,16 @@
         <f>VLOOKUP(A110,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L110" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M110" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>1000011458</v>
       </c>
@@ -14408,8 +15292,16 @@
         <f>VLOOKUP(A111,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L111" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M111" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>1000011460</v>
       </c>
@@ -14444,8 +15336,16 @@
         <f>VLOOKUP(A112,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L112" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M112" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>1000011461</v>
       </c>
@@ -14480,8 +15380,16 @@
         <f>VLOOKUP(A113,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L113" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M113" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>1000011462</v>
       </c>
@@ -14516,8 +15424,16 @@
         <f>VLOOKUP(A114,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L114" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M114" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>1000011464</v>
       </c>
@@ -14552,8 +15468,16 @@
         <f>VLOOKUP(A115,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L115" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M115" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>1000011465</v>
       </c>
@@ -14588,8 +15512,16 @@
         <f>VLOOKUP(A116,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L116" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M116" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>1000011466</v>
       </c>
@@ -14624,8 +15556,16 @@
         <f>VLOOKUP(A117,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L117" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M117" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>1000011467</v>
       </c>
@@ -14660,8 +15600,16 @@
         <f>VLOOKUP(A118,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L118" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M118" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>1000011469</v>
       </c>
@@ -14696,8 +15644,16 @@
         <f>VLOOKUP(A119,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L119" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M119" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>1000011470</v>
       </c>
@@ -14732,8 +15688,16 @@
         <f>VLOOKUP(A120,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L120" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M120" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>1000011471</v>
       </c>
@@ -14768,8 +15732,16 @@
         <f>VLOOKUP(A121,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L121" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M121" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>1000011472</v>
       </c>
@@ -14804,8 +15776,16 @@
         <f>VLOOKUP(A122,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L122" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M122" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>1000011473</v>
       </c>
@@ -14840,8 +15820,16 @@
         <f>VLOOKUP(A123,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L123" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M123" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>1000012409</v>
       </c>
@@ -14876,8 +15864,16 @@
         <f>VLOOKUP(A124,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L124" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M124" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>1000012410</v>
       </c>
@@ -14912,8 +15908,16 @@
         <f>VLOOKUP(A125,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L125" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M125" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>1000012415</v>
       </c>
@@ -14948,8 +15952,16 @@
         <f>VLOOKUP(A126,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L126" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M126" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>1000012423</v>
       </c>
@@ -14984,8 +15996,16 @@
         <f>VLOOKUP(A127,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L127" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M127" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>1000012425</v>
       </c>
@@ -15020,8 +16040,16 @@
         <f>VLOOKUP(A128,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L128" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M128" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>1000012426</v>
       </c>
@@ -15056,8 +16084,16 @@
         <f>VLOOKUP(A129,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L129" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M129" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>1000012427</v>
       </c>
@@ -15092,8 +16128,16 @@
         <f>VLOOKUP(A130,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L130" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M130" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>1000012429</v>
       </c>
@@ -15128,8 +16172,16 @@
         <f>VLOOKUP(A131,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L131" s="4">
+        <f t="shared" si="2"/>
+        <v>45901</v>
+      </c>
+      <c r="M131" s="4">
+        <f t="shared" si="3"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>1000012432</v>
       </c>
@@ -15164,8 +16216,16 @@
         <f>VLOOKUP(A132,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L132" s="4">
+        <f t="shared" ref="L132:L195" si="4">$L$2</f>
+        <v>45901</v>
+      </c>
+      <c r="M132" s="4">
+        <f t="shared" ref="M132:M195" si="5">$M$2</f>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>1000013208</v>
       </c>
@@ -15200,8 +16260,16 @@
         <f>VLOOKUP(A133,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L133" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M133" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>1000013214</v>
       </c>
@@ -15236,8 +16304,16 @@
         <f>VLOOKUP(A134,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L134" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M134" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>1000013427</v>
       </c>
@@ -15272,8 +16348,16 @@
         <f>VLOOKUP(A135,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L135" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M135" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>1000013440</v>
       </c>
@@ -15308,8 +16392,16 @@
         <f>VLOOKUP(A136,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L136" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M136" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>1000013465</v>
       </c>
@@ -15344,8 +16436,16 @@
         <f>VLOOKUP(A137,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L137" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M137" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>1000013487</v>
       </c>
@@ -15380,8 +16480,16 @@
         <f>VLOOKUP(A138,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L138" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M138" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>1000013508</v>
       </c>
@@ -15416,8 +16524,16 @@
         <f>VLOOKUP(A139,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L139" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M139" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>1000013619</v>
       </c>
@@ -15452,8 +16568,16 @@
         <f>VLOOKUP(A140,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L140" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M140" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>1000013620</v>
       </c>
@@ -15488,8 +16612,16 @@
         <f>VLOOKUP(A141,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L141" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M141" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>1000013734</v>
       </c>
@@ -15524,8 +16656,16 @@
         <f>VLOOKUP(A142,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L142" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M142" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>1000013785</v>
       </c>
@@ -15560,8 +16700,16 @@
         <f>VLOOKUP(A143,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L143" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M143" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>1000013860</v>
       </c>
@@ -15596,8 +16744,16 @@
         <f>VLOOKUP(A144,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L144" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M144" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>1000013877</v>
       </c>
@@ -15632,8 +16788,16 @@
         <f>VLOOKUP(A145,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L145" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M145" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>1000013878</v>
       </c>
@@ -15668,8 +16832,16 @@
         <f>VLOOKUP(A146,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L146" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M146" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>1000014074</v>
       </c>
@@ -15704,8 +16876,16 @@
         <f>VLOOKUP(A147,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L147" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M147" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>1000014200</v>
       </c>
@@ -15740,8 +16920,16 @@
         <f>VLOOKUP(A148,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L148" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M148" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>1000014215</v>
       </c>
@@ -15776,8 +16964,16 @@
         <f>VLOOKUP(A149,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L149" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M149" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>1000014331</v>
       </c>
@@ -15812,8 +17008,16 @@
         <f>VLOOKUP(A150,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L150" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M150" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>1000014370</v>
       </c>
@@ -15848,8 +17052,16 @@
         <f>VLOOKUP(A151,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L151" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M151" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>1000014460</v>
       </c>
@@ -15884,8 +17096,16 @@
         <f>VLOOKUP(A152,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L152" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M152" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>1000014463</v>
       </c>
@@ -15920,8 +17140,16 @@
         <f>VLOOKUP(A153,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L153" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M153" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>1000014616</v>
       </c>
@@ -15956,8 +17184,16 @@
         <f>VLOOKUP(A154,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L154" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M154" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>1000014621</v>
       </c>
@@ -15992,8 +17228,16 @@
         <f>VLOOKUP(A155,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L155" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M155" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>1000014626</v>
       </c>
@@ -16028,8 +17272,16 @@
         <f>VLOOKUP(A156,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L156" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M156" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>1000014823</v>
       </c>
@@ -16064,8 +17316,16 @@
         <f>VLOOKUP(A157,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L157" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M157" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>1000014912</v>
       </c>
@@ -16100,8 +17360,16 @@
         <f>VLOOKUP(A158,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L158" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M158" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>1000014996</v>
       </c>
@@ -16136,8 +17404,16 @@
         <f>VLOOKUP(A159,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L159" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M159" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>1000015083</v>
       </c>
@@ -16172,8 +17448,16 @@
         <f>VLOOKUP(A160,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L160" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M160" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>1000015122</v>
       </c>
@@ -16208,8 +17492,16 @@
         <f>VLOOKUP(A161,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L161" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M161" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>1000015127</v>
       </c>
@@ -16244,8 +17536,16 @@
         <f>VLOOKUP(A162,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L162" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M162" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>1000015133</v>
       </c>
@@ -16280,8 +17580,16 @@
         <f>VLOOKUP(A163,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L163" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M163" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>1000015161</v>
       </c>
@@ -16316,8 +17624,16 @@
         <f>VLOOKUP(A164,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L164" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M164" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>1000015178</v>
       </c>
@@ -16352,8 +17668,16 @@
         <f>VLOOKUP(A165,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L165" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M165" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>1000015232</v>
       </c>
@@ -16388,8 +17712,16 @@
         <f>VLOOKUP(A166,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L166" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M166" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>1000015251</v>
       </c>
@@ -16424,8 +17756,16 @@
         <f>VLOOKUP(A167,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L167" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M167" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>1000015283</v>
       </c>
@@ -16460,8 +17800,16 @@
         <f>VLOOKUP(A168,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L168" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M168" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>1000015502</v>
       </c>
@@ -16496,8 +17844,16 @@
         <f>VLOOKUP(A169,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L169" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M169" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>1000015515</v>
       </c>
@@ -16532,8 +17888,16 @@
         <f>VLOOKUP(A170,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L170" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M170" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>1000015524</v>
       </c>
@@ -16568,8 +17932,16 @@
         <f>VLOOKUP(A171,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L171" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M171" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>1000015560</v>
       </c>
@@ -16604,8 +17976,16 @@
         <f>VLOOKUP(A172,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L172" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M172" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>1000015599</v>
       </c>
@@ -16640,8 +18020,16 @@
         <f>VLOOKUP(A173,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L173" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M173" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>1000015600</v>
       </c>
@@ -16676,8 +18064,16 @@
         <f>VLOOKUP(A174,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L174" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M174" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>1000015602</v>
       </c>
@@ -16712,8 +18108,16 @@
         <f>VLOOKUP(A175,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L175" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M175" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>1000015665</v>
       </c>
@@ -16748,8 +18152,16 @@
         <f>VLOOKUP(A176,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L176" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M176" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>1000015666</v>
       </c>
@@ -16784,8 +18196,16 @@
         <f>VLOOKUP(A177,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L177" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M177" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>1000015694</v>
       </c>
@@ -16820,8 +18240,16 @@
         <f>VLOOKUP(A178,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L178" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M178" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>1000015727</v>
       </c>
@@ -16856,8 +18284,16 @@
         <f>VLOOKUP(A179,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L179" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M179" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>1000015791</v>
       </c>
@@ -16892,8 +18328,16 @@
         <f>VLOOKUP(A180,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L180" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M180" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>1000015891</v>
       </c>
@@ -16928,8 +18372,16 @@
         <f>VLOOKUP(A181,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L181" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M181" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>1000016003</v>
       </c>
@@ -16964,8 +18416,16 @@
         <f>VLOOKUP(A182,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L182" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M182" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>1000016023</v>
       </c>
@@ -17000,8 +18460,16 @@
         <f>VLOOKUP(A183,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L183" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M183" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>1000016264</v>
       </c>
@@ -17036,8 +18504,16 @@
         <f>VLOOKUP(A184,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L184" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M184" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>1000016363</v>
       </c>
@@ -17072,8 +18548,16 @@
         <f>VLOOKUP(A185,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L185" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M185" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>1000016811</v>
       </c>
@@ -17108,8 +18592,16 @@
         <f>VLOOKUP(A186,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L186" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M186" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>1000016823</v>
       </c>
@@ -17144,8 +18636,16 @@
         <f>VLOOKUP(A187,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L187" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M187" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>1000016842</v>
       </c>
@@ -17180,8 +18680,16 @@
         <f>VLOOKUP(A188,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L188" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M188" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>1000016860</v>
       </c>
@@ -17216,8 +18724,16 @@
         <f>VLOOKUP(A189,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L189" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M189" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>1000016864</v>
       </c>
@@ -17252,8 +18768,16 @@
         <f>VLOOKUP(A190,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L190" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M190" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>1000016876</v>
       </c>
@@ -17288,8 +18812,16 @@
         <f>VLOOKUP(A191,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L191" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M191" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>1000016877</v>
       </c>
@@ -17324,8 +18856,16 @@
         <f>VLOOKUP(A192,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L192" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M192" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>1000016878</v>
       </c>
@@ -17360,8 +18900,16 @@
         <f>VLOOKUP(A193,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L193" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M193" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>1000016901</v>
       </c>
@@ -17396,8 +18944,16 @@
         <f>VLOOKUP(A194,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L194" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M194" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>1000016903</v>
       </c>
@@ -17432,8 +18988,16 @@
         <f>VLOOKUP(A195,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L195" s="4">
+        <f t="shared" si="4"/>
+        <v>45901</v>
+      </c>
+      <c r="M195" s="4">
+        <f t="shared" si="5"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>1000016908</v>
       </c>
@@ -17468,8 +19032,16 @@
         <f>VLOOKUP(A196,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L196" s="4">
+        <f t="shared" ref="L196:L259" si="6">$L$2</f>
+        <v>45901</v>
+      </c>
+      <c r="M196" s="4">
+        <f t="shared" ref="M196:M259" si="7">$M$2</f>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>1000016924</v>
       </c>
@@ -17504,8 +19076,16 @@
         <f>VLOOKUP(A197,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L197" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M197" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>1000016930</v>
       </c>
@@ -17540,8 +19120,16 @@
         <f>VLOOKUP(A198,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L198" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M198" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>1000016963</v>
       </c>
@@ -17576,8 +19164,16 @@
         <f>VLOOKUP(A199,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L199" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M199" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>1000016980</v>
       </c>
@@ -17612,8 +19208,16 @@
         <f>VLOOKUP(A200,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L200" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M200" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>1000016990</v>
       </c>
@@ -17648,8 +19252,16 @@
         <f>VLOOKUP(A201,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L201" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M201" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>1000016992</v>
       </c>
@@ -17684,8 +19296,16 @@
         <f>VLOOKUP(A202,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L202" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M202" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>1000017000</v>
       </c>
@@ -17720,8 +19340,16 @@
         <f>VLOOKUP(A203,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L203" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M203" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>1000017002</v>
       </c>
@@ -17756,8 +19384,16 @@
         <f>VLOOKUP(A204,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L204" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M204" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>1000017029</v>
       </c>
@@ -17792,8 +19428,16 @@
         <f>VLOOKUP(A205,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L205" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M205" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>1000017031</v>
       </c>
@@ -17828,8 +19472,16 @@
         <f>VLOOKUP(A206,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L206" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M206" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>1000017033</v>
       </c>
@@ -17864,8 +19516,16 @@
         <f>VLOOKUP(A207,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L207" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M207" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>1000017128</v>
       </c>
@@ -17900,8 +19560,16 @@
         <f>VLOOKUP(A208,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L208" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M208" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>1000017189</v>
       </c>
@@ -17936,8 +19604,16 @@
         <f>VLOOKUP(A209,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L209" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M209" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>1000017190</v>
       </c>
@@ -17972,8 +19648,16 @@
         <f>VLOOKUP(A210,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L210" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M210" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>1000017245</v>
       </c>
@@ -18008,8 +19692,16 @@
         <f>VLOOKUP(A211,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L211" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M211" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>1000017249</v>
       </c>
@@ -18044,8 +19736,16 @@
         <f>VLOOKUP(A212,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L212" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M212" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>1000017251</v>
       </c>
@@ -18080,8 +19780,16 @@
         <f>VLOOKUP(A213,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L213" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M213" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>1000017257</v>
       </c>
@@ -18116,8 +19824,16 @@
         <f>VLOOKUP(A214,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L214" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M214" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>1000017268</v>
       </c>
@@ -18152,8 +19868,16 @@
         <f>VLOOKUP(A215,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L215" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M215" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>1000017347</v>
       </c>
@@ -18188,8 +19912,16 @@
         <f>VLOOKUP(A216,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L216" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M216" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>1000017369</v>
       </c>
@@ -18224,8 +19956,16 @@
         <f>VLOOKUP(A217,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L217" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M217" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>1000017370</v>
       </c>
@@ -18260,8 +20000,16 @@
         <f>VLOOKUP(A218,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L218" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M218" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>1000017378</v>
       </c>
@@ -18296,8 +20044,16 @@
         <f>VLOOKUP(A219,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L219" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M219" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>1000017397</v>
       </c>
@@ -18332,8 +20088,16 @@
         <f>VLOOKUP(A220,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L220" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M220" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>1000017398</v>
       </c>
@@ -18368,8 +20132,16 @@
         <f>VLOOKUP(A221,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L221" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M221" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>1000017411</v>
       </c>
@@ -18404,8 +20176,16 @@
         <f>VLOOKUP(A222,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L222" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M222" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>1000017412</v>
       </c>
@@ -18440,8 +20220,16 @@
         <f>VLOOKUP(A223,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L223" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M223" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>1000017436</v>
       </c>
@@ -18476,8 +20264,16 @@
         <f>VLOOKUP(A224,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L224" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M224" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>1000017446</v>
       </c>
@@ -18512,8 +20308,16 @@
         <f>VLOOKUP(A225,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L225" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M225" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>1000017467</v>
       </c>
@@ -18548,8 +20352,16 @@
         <f>VLOOKUP(A226,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L226" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M226" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>1000017474</v>
       </c>
@@ -18584,8 +20396,16 @@
         <f>VLOOKUP(A227,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L227" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M227" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>1000017532</v>
       </c>
@@ -18620,8 +20440,16 @@
         <f>VLOOKUP(A228,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L228" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M228" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>1000017548</v>
       </c>
@@ -18656,8 +20484,16 @@
         <f>VLOOKUP(A229,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L229" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M229" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>1000017550</v>
       </c>
@@ -18692,8 +20528,16 @@
         <f>VLOOKUP(A230,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L230" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M230" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>1000017660</v>
       </c>
@@ -18728,8 +20572,16 @@
         <f>VLOOKUP(A231,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L231" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M231" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>1000017696</v>
       </c>
@@ -18764,8 +20616,16 @@
         <f>VLOOKUP(A232,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L232" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M232" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>1000017709</v>
       </c>
@@ -18800,8 +20660,16 @@
         <f>VLOOKUP(A233,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L233" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M233" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>1000017778</v>
       </c>
@@ -18836,8 +20704,16 @@
         <f>VLOOKUP(A234,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L234" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M234" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>1000017848</v>
       </c>
@@ -18872,8 +20748,16 @@
         <f>VLOOKUP(A235,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L235" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M235" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>1000018025</v>
       </c>
@@ -18908,8 +20792,16 @@
         <f>VLOOKUP(A236,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L236" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M236" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>1000018027</v>
       </c>
@@ -18944,8 +20836,16 @@
         <f>VLOOKUP(A237,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L237" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M237" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>1000018117</v>
       </c>
@@ -18980,8 +20880,16 @@
         <f>VLOOKUP(A238,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L238" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M238" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>1000018160</v>
       </c>
@@ -19016,8 +20924,16 @@
         <f>VLOOKUP(A239,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L239" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M239" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>1000018247</v>
       </c>
@@ -19052,8 +20968,16 @@
         <f>VLOOKUP(A240,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L240" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M240" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>1000018406</v>
       </c>
@@ -19088,8 +21012,16 @@
         <f>VLOOKUP(A241,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L241" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M241" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>1000018448</v>
       </c>
@@ -19124,8 +21056,16 @@
         <f>VLOOKUP(A242,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L242" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M242" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>1000018450</v>
       </c>
@@ -19160,8 +21100,16 @@
         <f>VLOOKUP(A243,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L243" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M243" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>1000018461</v>
       </c>
@@ -19196,8 +21144,16 @@
         <f>VLOOKUP(A244,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L244" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M244" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>1000018462</v>
       </c>
@@ -19232,8 +21188,16 @@
         <f>VLOOKUP(A245,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L245" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M245" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>1000018467</v>
       </c>
@@ -19268,8 +21232,16 @@
         <f>VLOOKUP(A246,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L246" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M246" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>1000018552</v>
       </c>
@@ -19304,8 +21276,16 @@
         <f>VLOOKUP(A247,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L247" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M247" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>1000018593</v>
       </c>
@@ -19340,8 +21320,16 @@
         <f>VLOOKUP(A248,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L248" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M248" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>1000018594</v>
       </c>
@@ -19376,8 +21364,16 @@
         <f>VLOOKUP(A249,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L249" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M249" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>1000018596</v>
       </c>
@@ -19412,8 +21408,16 @@
         <f>VLOOKUP(A250,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L250" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M250" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>1000018646</v>
       </c>
@@ -19448,8 +21452,16 @@
         <f>VLOOKUP(A251,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L251" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M251" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>1000018677</v>
       </c>
@@ -19484,8 +21496,16 @@
         <f>VLOOKUP(A252,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L252" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M252" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>1000018695</v>
       </c>
@@ -19520,8 +21540,16 @@
         <f>VLOOKUP(A253,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L253" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M253" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>1000018697</v>
       </c>
@@ -19556,8 +21584,16 @@
         <f>VLOOKUP(A254,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L254" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M254" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>1000018698</v>
       </c>
@@ -19592,8 +21628,16 @@
         <f>VLOOKUP(A255,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L255" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M255" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>1000018699</v>
       </c>
@@ -19628,8 +21672,16 @@
         <f>VLOOKUP(A256,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L256" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M256" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>1000018700</v>
       </c>
@@ -19664,8 +21716,16 @@
         <f>VLOOKUP(A257,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L257" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M257" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>1000018726</v>
       </c>
@@ -19700,8 +21760,16 @@
         <f>VLOOKUP(A258,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L258" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M258" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>1000018746</v>
       </c>
@@ -19736,8 +21804,16 @@
         <f>VLOOKUP(A259,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L259" s="4">
+        <f t="shared" si="6"/>
+        <v>45901</v>
+      </c>
+      <c r="M259" s="4">
+        <f t="shared" si="7"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>1000018747</v>
       </c>
@@ -19772,8 +21848,16 @@
         <f>VLOOKUP(A260,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L260" s="4">
+        <f t="shared" ref="L260:L323" si="8">$L$2</f>
+        <v>45901</v>
+      </c>
+      <c r="M260" s="4">
+        <f t="shared" ref="M260:M323" si="9">$M$2</f>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>1000018843</v>
       </c>
@@ -19808,8 +21892,16 @@
         <f>VLOOKUP(A261,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L261" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M261" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>1000018844</v>
       </c>
@@ -19844,8 +21936,16 @@
         <f>VLOOKUP(A262,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L262" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M262" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>1000018849</v>
       </c>
@@ -19880,8 +21980,16 @@
         <f>VLOOKUP(A263,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L263" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M263" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>1000018860</v>
       </c>
@@ -19916,8 +22024,16 @@
         <f>VLOOKUP(A264,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L264" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M264" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>1000018861</v>
       </c>
@@ -19952,8 +22068,16 @@
         <f>VLOOKUP(A265,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L265" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M265" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>1000018875</v>
       </c>
@@ -19988,8 +22112,16 @@
         <f>VLOOKUP(A266,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L266" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M266" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>1000019108</v>
       </c>
@@ -20024,8 +22156,16 @@
         <f>VLOOKUP(A267,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L267" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M267" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>1000019165</v>
       </c>
@@ -20060,8 +22200,16 @@
         <f>VLOOKUP(A268,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L268" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M268" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>1000019166</v>
       </c>
@@ -20096,8 +22244,16 @@
         <f>VLOOKUP(A269,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L269" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M269" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>1000019207</v>
       </c>
@@ -20132,8 +22288,16 @@
         <f>VLOOKUP(A270,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L270" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M270" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>1000019218</v>
       </c>
@@ -20168,8 +22332,16 @@
         <f>VLOOKUP(A271,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L271" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M271" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>1000019226</v>
       </c>
@@ -20204,8 +22376,16 @@
         <f>VLOOKUP(A272,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L272" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M272" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>1000019333</v>
       </c>
@@ -20240,8 +22420,16 @@
         <f>VLOOKUP(A273,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L273" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M273" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>1000019423</v>
       </c>
@@ -20276,8 +22464,16 @@
         <f>VLOOKUP(A274,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L274" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M274" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>1000019424</v>
       </c>
@@ -20312,8 +22508,16 @@
         <f>VLOOKUP(A275,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L275" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M275" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>1000019426</v>
       </c>
@@ -20348,8 +22552,16 @@
         <f>VLOOKUP(A276,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L276" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M276" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>1000019555</v>
       </c>
@@ -20384,8 +22596,16 @@
         <f>VLOOKUP(A277,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L277" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M277" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>1000019564</v>
       </c>
@@ -20420,8 +22640,16 @@
         <f>VLOOKUP(A278,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L278" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M278" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>1000019565</v>
       </c>
@@ -20456,8 +22684,16 @@
         <f>VLOOKUP(A279,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L279" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M279" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>1000019577</v>
       </c>
@@ -20492,8 +22728,16 @@
         <f>VLOOKUP(A280,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L280" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M280" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>1000019633</v>
       </c>
@@ -20528,8 +22772,16 @@
         <f>VLOOKUP(A281,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L281" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M281" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>1000019637</v>
       </c>
@@ -20564,8 +22816,16 @@
         <f>VLOOKUP(A282,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L282" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M282" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>1000019707</v>
       </c>
@@ -20600,8 +22860,16 @@
         <f>VLOOKUP(A283,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L283" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M283" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>1000019712</v>
       </c>
@@ -20636,8 +22904,16 @@
         <f>VLOOKUP(A284,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L284" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M284" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>1000019822</v>
       </c>
@@ -20672,8 +22948,16 @@
         <f>VLOOKUP(A285,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L285" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M285" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>1000019823</v>
       </c>
@@ -20708,8 +22992,16 @@
         <f>VLOOKUP(A286,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L286" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M286" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>1000019824</v>
       </c>
@@ -20744,8 +23036,16 @@
         <f>VLOOKUP(A287,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L287" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M287" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>1000019830</v>
       </c>
@@ -20780,8 +23080,16 @@
         <f>VLOOKUP(A288,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L288" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M288" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>1000019851</v>
       </c>
@@ -20816,8 +23124,16 @@
         <f>VLOOKUP(A289,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L289" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M289" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>1000019874</v>
       </c>
@@ -20852,8 +23168,16 @@
         <f>VLOOKUP(A290,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L290" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M290" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>1000019875</v>
       </c>
@@ -20888,8 +23212,16 @@
         <f>VLOOKUP(A291,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L291" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M291" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>1000019876</v>
       </c>
@@ -20924,8 +23256,16 @@
         <f>VLOOKUP(A292,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L292" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M292" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>1000019877</v>
       </c>
@@ -20960,8 +23300,16 @@
         <f>VLOOKUP(A293,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L293" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M293" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>1000019918</v>
       </c>
@@ -20996,8 +23344,16 @@
         <f>VLOOKUP(A294,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L294" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M294" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>1000020102</v>
       </c>
@@ -21032,8 +23388,16 @@
         <f>VLOOKUP(A295,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L295" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M295" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>1000020109</v>
       </c>
@@ -21068,8 +23432,16 @@
         <f>VLOOKUP(A296,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L296" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M296" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>1000020151</v>
       </c>
@@ -21104,8 +23476,16 @@
         <f>VLOOKUP(A297,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L297" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M297" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>1000020152</v>
       </c>
@@ -21140,8 +23520,16 @@
         <f>VLOOKUP(A298,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L298" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M298" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>1000020166</v>
       </c>
@@ -21176,8 +23564,16 @@
         <f>VLOOKUP(A299,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L299" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M299" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>1000020192</v>
       </c>
@@ -21212,8 +23608,16 @@
         <f>VLOOKUP(A300,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L300" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M300" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>1000020193</v>
       </c>
@@ -21248,8 +23652,16 @@
         <f>VLOOKUP(A301,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L301" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M301" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>1000020201</v>
       </c>
@@ -21284,8 +23696,16 @@
         <f>VLOOKUP(A302,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L302" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M302" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>1000020224</v>
       </c>
@@ -21320,8 +23740,16 @@
         <f>VLOOKUP(A303,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L303" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M303" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>1000020225</v>
       </c>
@@ -21356,8 +23784,16 @@
         <f>VLOOKUP(A304,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L304" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M304" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>1000020226</v>
       </c>
@@ -21392,8 +23828,16 @@
         <f>VLOOKUP(A305,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L305" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M305" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>1000020235</v>
       </c>
@@ -21428,8 +23872,16 @@
         <f>VLOOKUP(A306,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L306" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M306" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>1000020245</v>
       </c>
@@ -21464,8 +23916,16 @@
         <f>VLOOKUP(A307,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L307" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M307" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>1000020262</v>
       </c>
@@ -21500,8 +23960,16 @@
         <f>VLOOKUP(A308,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L308" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M308" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>1000020289</v>
       </c>
@@ -21536,8 +24004,16 @@
         <f>VLOOKUP(A309,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L309" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M309" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>1000020313</v>
       </c>
@@ -21572,8 +24048,16 @@
         <f>VLOOKUP(A310,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L310" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M310" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>1000020331</v>
       </c>
@@ -21608,8 +24092,16 @@
         <f>VLOOKUP(A311,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L311" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M311" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>1000020355</v>
       </c>
@@ -21644,8 +24136,16 @@
         <f>VLOOKUP(A312,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L312" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M312" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>1000020442</v>
       </c>
@@ -21680,8 +24180,16 @@
         <f>VLOOKUP(A313,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L313" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M313" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>1000020444</v>
       </c>
@@ -21716,8 +24224,16 @@
         <f>VLOOKUP(A314,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L314" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M314" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>1000020447</v>
       </c>
@@ -21752,8 +24268,16 @@
         <f>VLOOKUP(A315,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L315" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M315" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>1000020449</v>
       </c>
@@ -21788,8 +24312,16 @@
         <f>VLOOKUP(A316,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L316" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M316" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>1000020464</v>
       </c>
@@ -21824,8 +24356,16 @@
         <f>VLOOKUP(A317,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L317" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M317" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>1000020581</v>
       </c>
@@ -21860,8 +24400,16 @@
         <f>VLOOKUP(A318,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L318" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M318" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>1000020650</v>
       </c>
@@ -21896,8 +24444,16 @@
         <f>VLOOKUP(A319,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L319" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M319" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>1000020732</v>
       </c>
@@ -21932,8 +24488,16 @@
         <f>VLOOKUP(A320,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L320" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M320" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>1000020816</v>
       </c>
@@ -21968,8 +24532,16 @@
         <f>VLOOKUP(A321,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L321" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M321" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>1000020921</v>
       </c>
@@ -22004,8 +24576,16 @@
         <f>VLOOKUP(A322,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L322" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M322" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>1000020922</v>
       </c>
@@ -22040,8 +24620,16 @@
         <f>VLOOKUP(A323,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L323" s="4">
+        <f t="shared" si="8"/>
+        <v>45901</v>
+      </c>
+      <c r="M323" s="4">
+        <f t="shared" si="9"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>1000020928</v>
       </c>
@@ -22076,8 +24664,16 @@
         <f>VLOOKUP(A324,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L324" s="4">
+        <f t="shared" ref="L324:L385" si="10">$L$2</f>
+        <v>45901</v>
+      </c>
+      <c r="M324" s="4">
+        <f t="shared" ref="M324:M385" si="11">$M$2</f>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>1000021031</v>
       </c>
@@ -22112,8 +24708,16 @@
         <f>VLOOKUP(A325,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L325" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M325" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>1000021041</v>
       </c>
@@ -22148,8 +24752,16 @@
         <f>VLOOKUP(A326,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L326" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M326" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>1000021112</v>
       </c>
@@ -22184,8 +24796,16 @@
         <f>VLOOKUP(A327,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L327" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M327" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>1000021117</v>
       </c>
@@ -22220,8 +24840,16 @@
         <f>VLOOKUP(A328,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L328" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M328" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>1000021118</v>
       </c>
@@ -22256,8 +24884,16 @@
         <f>VLOOKUP(A329,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L329" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M329" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>1000021119</v>
       </c>
@@ -22292,8 +24928,16 @@
         <f>VLOOKUP(A330,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L330" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M330" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>1000021160</v>
       </c>
@@ -22328,8 +24972,16 @@
         <f>VLOOKUP(A331,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L331" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M331" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>1000021178</v>
       </c>
@@ -22364,8 +25016,16 @@
         <f>VLOOKUP(A332,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L332" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M332" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>1000021233</v>
       </c>
@@ -22400,8 +25060,16 @@
         <f>VLOOKUP(A333,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L333" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M333" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>1000021256</v>
       </c>
@@ -22436,8 +25104,16 @@
         <f>VLOOKUP(A334,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L334" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M334" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>1000021272</v>
       </c>
@@ -22472,8 +25148,16 @@
         <f>VLOOKUP(A335,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L335" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M335" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>1000021288</v>
       </c>
@@ -22508,8 +25192,16 @@
         <f>VLOOKUP(A336,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L336" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M336" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>1000021302</v>
       </c>
@@ -22544,8 +25236,16 @@
         <f>VLOOKUP(A337,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L337" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M337" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>1000021303</v>
       </c>
@@ -22580,8 +25280,16 @@
         <f>VLOOKUP(A338,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L338" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M338" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>1000021337</v>
       </c>
@@ -22616,8 +25324,16 @@
         <f>VLOOKUP(A339,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L339" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M339" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>1000021351</v>
       </c>
@@ -22652,8 +25368,16 @@
         <f>VLOOKUP(A340,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L340" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M340" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>1000021670</v>
       </c>
@@ -22688,8 +25412,16 @@
         <f>VLOOKUP(A341,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L341" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M341" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>1000021690</v>
       </c>
@@ -22724,8 +25456,16 @@
         <f>VLOOKUP(A342,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L342" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M342" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>1000021708</v>
       </c>
@@ -22760,8 +25500,16 @@
         <f>VLOOKUP(A343,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L343" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M343" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>1000021731</v>
       </c>
@@ -22796,8 +25544,16 @@
         <f>VLOOKUP(A344,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L344" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M344" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>1000021990</v>
       </c>
@@ -22832,8 +25588,16 @@
         <f>VLOOKUP(A345,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L345" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M345" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>1000022013</v>
       </c>
@@ -22868,8 +25632,16 @@
         <f>VLOOKUP(A346,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L346" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M346" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>1000022014</v>
       </c>
@@ -22904,8 +25676,16 @@
         <f>VLOOKUP(A347,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L347" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M347" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>1000022015</v>
       </c>
@@ -22940,8 +25720,16 @@
         <f>VLOOKUP(A348,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L348" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M348" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>1000022041</v>
       </c>
@@ -22976,8 +25764,16 @@
         <f>VLOOKUP(A349,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L349" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M349" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>1000022052</v>
       </c>
@@ -23012,8 +25808,16 @@
         <f>VLOOKUP(A350,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L350" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M350" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>1000022062</v>
       </c>
@@ -23048,8 +25852,16 @@
         <f>VLOOKUP(A351,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L351" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M351" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>1000022090</v>
       </c>
@@ -23084,8 +25896,16 @@
         <f>VLOOKUP(A352,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L352" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M352" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="353" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>1000022103</v>
       </c>
@@ -23120,8 +25940,16 @@
         <f>VLOOKUP(A353,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L353" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M353" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>1000022104</v>
       </c>
@@ -23156,8 +25984,16 @@
         <f>VLOOKUP(A354,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L354" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M354" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>1000022137</v>
       </c>
@@ -23192,8 +26028,16 @@
         <f>VLOOKUP(A355,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L355" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M355" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="356" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>1000022179</v>
       </c>
@@ -23228,8 +26072,16 @@
         <f>VLOOKUP(A356,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L356" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M356" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="357" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>1000022180</v>
       </c>
@@ -23264,8 +26116,16 @@
         <f>VLOOKUP(A357,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L357" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M357" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="358" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>1000022275</v>
       </c>
@@ -23300,8 +26160,16 @@
         <f>VLOOKUP(A358,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L358" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M358" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>1000022302</v>
       </c>
@@ -23336,8 +26204,16 @@
         <f>VLOOKUP(A359,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L359" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M359" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="360" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>1000022305</v>
       </c>
@@ -23372,8 +26248,16 @@
         <f>VLOOKUP(A360,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L360" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M360" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="361" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>1000022306</v>
       </c>
@@ -23408,8 +26292,16 @@
         <f>VLOOKUP(A361,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L361" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M361" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="362" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>1000022329</v>
       </c>
@@ -23444,8 +26336,16 @@
         <f>VLOOKUP(A362,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L362" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M362" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>1000022330</v>
       </c>
@@ -23480,8 +26380,16 @@
         <f>VLOOKUP(A363,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L363" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M363" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>1000022331</v>
       </c>
@@ -23516,8 +26424,16 @@
         <f>VLOOKUP(A364,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L364" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M364" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="365" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>1000022360</v>
       </c>
@@ -23552,8 +26468,16 @@
         <f>VLOOKUP(A365,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L365" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M365" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>1000022370</v>
       </c>
@@ -23588,8 +26512,16 @@
         <f>VLOOKUP(A366,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L366" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M366" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="367" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>1000022384</v>
       </c>
@@ -23624,8 +26556,16 @@
         <f>VLOOKUP(A367,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L367" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M367" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>1000022419</v>
       </c>
@@ -23660,8 +26600,16 @@
         <f>VLOOKUP(A368,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L368" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M368" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>1000022420</v>
       </c>
@@ -23696,8 +26644,16 @@
         <f>VLOOKUP(A369,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L369" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M369" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>1000022421</v>
       </c>
@@ -23732,8 +26688,16 @@
         <f>VLOOKUP(A370,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L370" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M370" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>1000022422</v>
       </c>
@@ -23768,8 +26732,16 @@
         <f>VLOOKUP(A371,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L371" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M371" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="372" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>1000022472</v>
       </c>
@@ -23804,8 +26776,16 @@
         <f>VLOOKUP(A372,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L372" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M372" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>1000022488</v>
       </c>
@@ -23840,8 +26820,16 @@
         <f>VLOOKUP(A373,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L373" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M373" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>1000022531</v>
       </c>
@@ -23876,8 +26864,16 @@
         <f>VLOOKUP(A374,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L374" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M374" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="375" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>1000022532</v>
       </c>
@@ -23912,8 +26908,16 @@
         <f>VLOOKUP(A375,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L375" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M375" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="376" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>1000022533</v>
       </c>
@@ -23948,8 +26952,16 @@
         <f>VLOOKUP(A376,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L376" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M376" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="377" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>1000022549</v>
       </c>
@@ -23984,8 +26996,16 @@
         <f>VLOOKUP(A377,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L377" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M377" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>1000022551</v>
       </c>
@@ -24020,8 +27040,16 @@
         <f>VLOOKUP(A378,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Southern</v>
       </c>
-    </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L378" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M378" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>1000022569</v>
       </c>
@@ -24056,8 +27084,16 @@
         <f>VLOOKUP(A379,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L379" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M379" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="380" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>1000022638</v>
       </c>
@@ -24092,8 +27128,16 @@
         <f>VLOOKUP(A380,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Western</v>
       </c>
-    </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L380" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M380" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="381" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>1000022709</v>
       </c>
@@ -24128,8 +27172,16 @@
         <f>VLOOKUP(A381,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L381" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M381" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="382" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>1000022710</v>
       </c>
@@ -24164,8 +27216,16 @@
         <f>VLOOKUP(A382,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L382" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M382" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>1000022754</v>
       </c>
@@ -24200,8 +27260,16 @@
         <f>VLOOKUP(A383,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
       </c>
-    </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L383" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M383" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="384" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>1000022783</v>
       </c>
@@ -24236,8 +27304,16 @@
         <f>VLOOKUP(A384,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Northern</v>
       </c>
-    </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L384" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M384" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>1000022787</v>
       </c>
@@ -24271,6 +27347,14 @@
       <c r="K385" s="3" t="str">
         <f>VLOOKUP(A385,[1]Sheet1!$A$2:$F$385,6,FALSE)</f>
         <v>Eastern</v>
+      </c>
+      <c r="L385" s="4">
+        <f t="shared" si="10"/>
+        <v>45901</v>
+      </c>
+      <c r="M385" s="4">
+        <f t="shared" si="11"/>
+        <v>46292</v>
       </c>
     </row>
   </sheetData>
